--- a/data/trans_camb/P19C05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C05-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 4,4</t>
+          <t>-10,82; 4,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,6; -6,96</t>
+          <t>-19,82; -6,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -2,36</t>
+          <t>-15,11; -1,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 6,39</t>
+          <t>-7,18; 6,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -1,37</t>
+          <t>-15,15; -2,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,4; -2,58</t>
+          <t>-13,32; -2,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 3,9</t>
+          <t>-6,87; 4,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,93; -5,92</t>
+          <t>-14,48; -5,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,5; -4,09</t>
+          <t>-12,78; -4,23</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,64; 32,97</t>
+          <t>-47,91; 33,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,78; -44,3</t>
+          <t>-85,98; -47,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-66,05; -17,29</t>
+          <t>-67,13; -13,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,32; 57,06</t>
+          <t>-35,52; 56,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,59; -6,96</t>
+          <t>-73,24; -16,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,96; -19,72</t>
+          <t>-66,64; -16,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 29,69</t>
+          <t>-34,83; 27,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,97; -40,88</t>
+          <t>-74,46; -40,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-62,63; -28,62</t>
+          <t>-63,76; -29,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 2,07</t>
+          <t>-7,39; 2,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 4,47</t>
+          <t>-5,79; 4,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,26; -2,67</t>
+          <t>-11,01; -2,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 7,63</t>
+          <t>-2,58; 7,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 6,61</t>
+          <t>-3,12; 6,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 3,23</t>
+          <t>-4,07; 3,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 3,49</t>
+          <t>-3,52; 3,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,87</t>
+          <t>-3,18; 4,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -0,44</t>
+          <t>-6,65; -0,63</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,71; 17,32</t>
+          <t>-45,02; 21,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,42; 39,57</t>
+          <t>-34,9; 38,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,5; -20,26</t>
+          <t>-64,48; -20,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 68,25</t>
+          <t>-16,81; 66,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,16; 60,97</t>
+          <t>-20,64; 60,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 29,18</t>
+          <t>-26,2; 30,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 28,3</t>
+          <t>-22,37; 29,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 33,12</t>
+          <t>-20,46; 34,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,83; -3,57</t>
+          <t>-42,6; -4,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 9,66</t>
+          <t>-2,59; 9,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 3,21</t>
+          <t>-8,01; 3,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 3,92</t>
+          <t>-7,52; 3,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 6,8</t>
+          <t>-7,45; 6,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,18; -7,87</t>
+          <t>-20,11; -8,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,22; -2,22</t>
+          <t>-14,58; -3,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 5,67</t>
+          <t>-3,53; 5,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,6; -4,18</t>
+          <t>-12,93; -4,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,2; -1,88</t>
+          <t>-9,82; -1,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 98,11</t>
+          <t>-16,88; 101,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-46,93; 33,1</t>
+          <t>-48,12; 39,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,85; 40,58</t>
+          <t>-44,08; 34,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,69; 34,33</t>
+          <t>-26,88; 32,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,57; -37,36</t>
+          <t>-73,25; -37,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,43; -12,25</t>
+          <t>-52,78; -17,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 35,26</t>
+          <t>-16,56; 35,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,28; -25,42</t>
+          <t>-59,67; -25,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-46,14; -11,32</t>
+          <t>-45,78; -11,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 4,34</t>
+          <t>-7,56; 4,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 3,11</t>
+          <t>-8,8; 2,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 2,16</t>
+          <t>-9,89; 1,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 1,59</t>
+          <t>-11,14; 1,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 0,75</t>
+          <t>-12,36; -0,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,91; -6,83</t>
+          <t>-18,43; -6,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 0,83</t>
+          <t>-8,51; 0,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,73; -0,17</t>
+          <t>-9,54; -0,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,67; -4,76</t>
+          <t>-13,01; -4,35</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,75; 34,39</t>
+          <t>-38,47; 35,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,95; 24,02</t>
+          <t>-46,68; 21,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,67; 16,85</t>
+          <t>-49,31; 14,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,41; 9,88</t>
+          <t>-42,43; 9,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,66; 4,41</t>
+          <t>-47,8; 1,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,19; -36,3</t>
+          <t>-71,78; -35,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,33; 5,56</t>
+          <t>-38,29; 2,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,18; -0,04</t>
+          <t>-43,12; -4,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-62,33; -27,99</t>
+          <t>-59,02; -24,82</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 15,77</t>
+          <t>2,65; 17,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 14,78</t>
+          <t>-1,13; 14,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 8,31</t>
+          <t>-2,89; 7,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 10,99</t>
+          <t>-3,33; 11,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 12,77</t>
+          <t>-4,0; 11,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 13,67</t>
+          <t>0,84; 13,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,59; 11,46</t>
+          <t>1,98; 11,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 10,8</t>
+          <t>-0,39; 11,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 9,84</t>
+          <t>1,54; 10,26</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>15,2; 255,26</t>
+          <t>20,91; 287,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 226,52</t>
+          <t>-14,45; 219,71</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-28,21; 144,37</t>
+          <t>-28,61; 149,54</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 114,26</t>
+          <t>-21,21; 124,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 128,07</t>
+          <t>-26,5; 118,59</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,22; 146,08</t>
+          <t>4,12; 146,36</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,32; 130,99</t>
+          <t>13,2; 135,0</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 118,91</t>
+          <t>-5,3; 122,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6,49; 112,47</t>
+          <t>8,54; 122,81</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-15,23; -1,13</t>
+          <t>-14,09; -1,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,87; -5,56</t>
+          <t>-18,96; -6,09</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,07; -0,35</t>
+          <t>-13,33; -0,72</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 12,05</t>
+          <t>-2,45; 11,77</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-16,12; -3,62</t>
+          <t>-15,45; -3,17</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 0,38</t>
+          <t>-10,37; 1,03</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 3,82</t>
+          <t>-6,09; 3,15</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-15,37; -6,3</t>
+          <t>-15,34; -6,57</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,68; -1,38</t>
+          <t>-10,61; -1,63</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-63,77; -7,61</t>
+          <t>-61,88; -6,57</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-79,03; -34,22</t>
+          <t>-79,28; -38,41</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-54,97; -2,13</t>
+          <t>-55,12; -2,28</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 94,05</t>
+          <t>-13,13; 97,86</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-79,7; -25,69</t>
+          <t>-77,8; -24,59</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-53,54; 3,49</t>
+          <t>-52,05; 8,46</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 25,8</t>
+          <t>-29,58; 23,59</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-74,51; -40,42</t>
+          <t>-74,39; -41,64</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-47,32; -8,68</t>
+          <t>-49,49; -10,71</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 9,22</t>
+          <t>-0,8; 9,18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,79; -3,29</t>
+          <t>-11,32; -2,9</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 1,33</t>
+          <t>-7,28; 1,47</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,65; 10,98</t>
+          <t>1,32; 10,49</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,74; -2,21</t>
+          <t>-10,28; -1,73</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-12,21; -1,53</t>
+          <t>-12,69; -1,83</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,92; 8,66</t>
+          <t>2,09; 8,44</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-9,53; -3,58</t>
+          <t>-9,85; -3,76</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-9,33; -1,5</t>
+          <t>-9,7; -1,54</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 73,83</t>
+          <t>-3,6; 71,18</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-64,39; -20,34</t>
+          <t>-63,52; -20,63</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 10,54</t>
+          <t>-40,37; 11,97</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,74; 83,63</t>
+          <t>6,91; 80,54</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-60,84; -15,74</t>
+          <t>-58,97; -13,07</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-71,65; -12,82</t>
+          <t>-77,0; -13,87</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,96; 62,39</t>
+          <t>11,34; 61,51</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-57,13; -24,85</t>
+          <t>-57,75; -26,88</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-56,53; -11,6</t>
+          <t>-57,7; -11,37</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,12; 8,61</t>
+          <t>0,51; 8,15</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,19; 7,34</t>
+          <t>-0,02; 7,12</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 0,98</t>
+          <t>-7,22; 0,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 6,57</t>
+          <t>-1,57; 6,58</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 2,57</t>
+          <t>-5,05; 2,67</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,43; -0,6</t>
+          <t>-7,18; -0,79</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,85; 6,13</t>
+          <t>0,64; 6,37</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,58</t>
+          <t>-1,52; 3,78</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-7,35; -0,89</t>
+          <t>-6,88; -0,88</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>10,99; 127,2</t>
+          <t>4,77; 120,2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2,04; 109,09</t>
+          <t>0,69; 110,05</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-68,68; 13,03</t>
+          <t>-69,16; 10,27</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 57,69</t>
+          <t>-10,77; 59,89</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-33,01; 23,63</t>
+          <t>-31,61; 24,35</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-46,95; -5,12</t>
+          <t>-45,94; -7,15</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,02; 65,45</t>
+          <t>5,36; 67,97</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 37,67</t>
+          <t>-12,56; 39,3</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-62,02; -10,26</t>
+          <t>-58,37; -9,72</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,33</t>
+          <t>-0,56; 3,1</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,86; -1,13</t>
+          <t>-4,66; -1,24</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,43; -2,15</t>
+          <t>-6,82; -2,38</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,98</t>
+          <t>0,12; 4,18</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,21; -2,58</t>
+          <t>-6,38; -2,67</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,53; -3,12</t>
+          <t>-7,37; -3,15</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,25</t>
+          <t>0,34; 3,1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -2,46</t>
+          <t>-5,13; -2,42</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-6,34; -3,25</t>
+          <t>-6,17; -3,27</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 26,18</t>
+          <t>-3,9; 24,38</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-33,01; -8,87</t>
+          <t>-32,58; -9,71</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -17,27</t>
+          <t>-46,88; -18,62</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>0,86; 26,31</t>
+          <t>0,72; 27,54</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-36,72; -16,71</t>
+          <t>-37,63; -17,64</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -20,92</t>
+          <t>-44,52; -21,06</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,8; 22,8</t>
+          <t>2,17; 21,78</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-32,03; -16,88</t>
+          <t>-32,71; -16,9</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-40,98; -22,72</t>
+          <t>-40,68; -22,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C05-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-8,63</t>
+          <t>-7,81</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-7,53</t>
+          <t>-8,02</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-8,02</t>
+          <t>-7,9</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 4,58</t>
+          <t>-10,77; 4,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,82; -6,97</t>
+          <t>-19,45; -7,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,11; -1,93</t>
+          <t>-14,41; -1,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 6,53</t>
+          <t>-6,79; 6,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,15; -2,05</t>
+          <t>-13,31; -1,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,32; -2,07</t>
+          <t>-13,61; -2,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 4,0</t>
+          <t>-6,84; 4,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,48; -5,86</t>
+          <t>-14,45; -5,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,78; -4,23</t>
+          <t>-12,19; -3,88</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-47,32%</t>
+          <t>-42,82%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-48,83%</t>
+          <t>-52,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-47,75%</t>
+          <t>-47,06%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,91; 33,69</t>
+          <t>-47,95; 35,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,98; -47,26</t>
+          <t>-86,22; -46,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,13; -13,46</t>
+          <t>-63,17; -9,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,52; 56,46</t>
+          <t>-37,13; 57,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,24; -16,27</t>
+          <t>-68,63; -8,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,64; -16,28</t>
+          <t>-68,83; -23,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 27,71</t>
+          <t>-33,9; 29,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,46; -40,13</t>
+          <t>-73,66; -40,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-63,76; -29,41</t>
+          <t>-60,88; -26,78</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,67</t>
+          <t>-6,11</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,51</t>
+          <t>-3,13</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 2,36</t>
+          <t>-8,31; 1,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 4,66</t>
+          <t>-6,08; 4,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,01; -2,53</t>
+          <t>-10,82; -1,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 7,44</t>
+          <t>-2,34; 7,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 6,7</t>
+          <t>-3,79; 6,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 3,41</t>
+          <t>-4,4; 3,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 3,62</t>
+          <t>-3,34; 3,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 4,11</t>
+          <t>-3,0; 4,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,65; -0,63</t>
+          <t>-6,1; -0,14</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-46,88%</t>
+          <t>-43,01%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-2,65%</t>
+          <t>-1,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-25,37%</t>
+          <t>-22,61%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,02; 21,1</t>
+          <t>-47,92; 17,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 38,5</t>
+          <t>-36,3; 37,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-64,48; -20,71</t>
+          <t>-62,85; -15,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 66,43</t>
+          <t>-14,32; 65,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 60,99</t>
+          <t>-23,13; 54,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,2; 30,18</t>
+          <t>-27,44; 33,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 29,61</t>
+          <t>-22,22; 31,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 34,26</t>
+          <t>-19,53; 36,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,6; -4,55</t>
+          <t>-38,97; -1,12</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>-1,9</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-9,0</t>
+          <t>-8,88</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-5,83</t>
+          <t>-5,8</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 9,99</t>
+          <t>-2,74; 9,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 3,67</t>
+          <t>-7,54; 4,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 3,4</t>
+          <t>-7,12; 2,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 6,43</t>
+          <t>-7,56; 6,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,11; -8,11</t>
+          <t>-19,48; -7,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,58; -3,75</t>
+          <t>-14,83; -3,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 5,76</t>
+          <t>-3,63; 6,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -4,1</t>
+          <t>-12,29; -4,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -1,77</t>
+          <t>-9,84; -2,03</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-13,61%</t>
+          <t>-14,43%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-38,1%</t>
+          <t>-37,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-30,8%</t>
+          <t>-30,64%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 101,82</t>
+          <t>-15,19; 105,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 39,35</t>
+          <t>-45,82; 42,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,08; 34,56</t>
+          <t>-42,24; 29,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 32,77</t>
+          <t>-27,3; 30,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,25; -37,72</t>
+          <t>-72,89; -37,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,78; -17,95</t>
+          <t>-53,46; -16,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 35,24</t>
+          <t>-17,42; 38,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,67; -25,05</t>
+          <t>-58,71; -25,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-45,78; -11,51</t>
+          <t>-45,47; -11,98</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-4,1</t>
+          <t>-4,58</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-12,14</t>
+          <t>-9,91</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-8,49</t>
+          <t>-7,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 4,06</t>
+          <t>-7,94; 3,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 2,91</t>
+          <t>-8,8; 3,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 1,81</t>
+          <t>-10,34; 1,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 1,38</t>
+          <t>-11,45; 1,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,36; -0,04</t>
+          <t>-12,29; 0,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,43; -6,68</t>
+          <t>-15,5; -4,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 0,49</t>
+          <t>-7,86; 0,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -0,92</t>
+          <t>-8,75; -0,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,01; -4,35</t>
+          <t>-11,78; -3,86</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-25,19%</t>
+          <t>-28,14%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-54,14%</t>
+          <t>-44,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-43,48%</t>
+          <t>-37,86%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,47; 35,55</t>
+          <t>-41,65; 26,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 21,84</t>
+          <t>-45,46; 24,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,31; 14,15</t>
+          <t>-51,39; 9,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,43; 9,2</t>
+          <t>-43,95; 8,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 1,49</t>
+          <t>-48,32; 5,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-71,78; -35,5</t>
+          <t>-57,8; -23,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-38,29; 2,95</t>
+          <t>-35,5; 3,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-43,12; -4,42</t>
+          <t>-40,63; -1,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,02; -24,82</t>
+          <t>-52,87; -22,08</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>1,9</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,84</t>
+          <t>6,97</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,66</t>
+          <t>4,77</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,65; 17,51</t>
+          <t>1,6; 16,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 14,19</t>
+          <t>-1,64; 13,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 7,91</t>
+          <t>-3,73; 6,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 11,13</t>
+          <t>-3,2; 12,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 11,65</t>
+          <t>-4,17; 12,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 13,43</t>
+          <t>0,6; 12,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,96</t>
+          <t>1,3; 11,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 11,07</t>
+          <t>0,44; 11,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 10,26</t>
+          <t>0,57; 8,76</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>20,91; 287,84</t>
+          <t>12,91; 305,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 219,71</t>
+          <t>-18,46; 216,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 149,54</t>
+          <t>-32,75; 115,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 124,43</t>
+          <t>-19,2; 130,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 118,59</t>
+          <t>-23,19; 135,93</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,12; 146,36</t>
+          <t>2,31; 132,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,2; 135,0</t>
+          <t>8,84; 138,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 122,52</t>
+          <t>0,85; 125,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8,54; 122,81</t>
+          <t>3,29; 102,36</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-6,75</t>
+          <t>-6,57</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,79</t>
+          <t>-4,9</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,69</t>
+          <t>-5,67</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-14,09; -1,03</t>
+          <t>-15,26; -0,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,96; -6,09</t>
+          <t>-19,93; -6,35</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,33; -0,72</t>
+          <t>-13,15; -0,22</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 11,77</t>
+          <t>-2,59; 11,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,45; -3,17</t>
+          <t>-15,27; -3,3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 1,03</t>
+          <t>-11,01; 0,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 3,15</t>
+          <t>-6,09; 3,55</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-15,34; -6,57</t>
+          <t>-15,47; -6,51</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-10,61; -1,63</t>
+          <t>-10,37; -1,6</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-34,73%</t>
+          <t>-33,79%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-30,07%</t>
+          <t>-30,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-32,3%</t>
+          <t>-32,17%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-61,88; -6,57</t>
+          <t>-63,51; -3,89</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-79,28; -38,41</t>
+          <t>-81,01; -36,91</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-55,12; -2,28</t>
+          <t>-54,23; -1,07</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 97,86</t>
+          <t>-13,67; 94,1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-77,8; -24,59</t>
+          <t>-77,31; -22,21</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-52,05; 8,46</t>
+          <t>-53,96; 4,97</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-29,58; 23,59</t>
+          <t>-30,28; 25,8</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-74,39; -41,64</t>
+          <t>-74,69; -42,81</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-49,49; -10,71</t>
+          <t>-49,26; -10,83</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-2,71</t>
+          <t>-2,42</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-6,16</t>
+          <t>-2,64</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-4,71</t>
+          <t>-2,53</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 9,18</t>
+          <t>-0,31; 9,44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,32; -2,9</t>
+          <t>-11,25; -2,8</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 1,47</t>
+          <t>-6,97; 1,69</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,32; 10,49</t>
+          <t>1,28; 10,55</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,28; -1,73</t>
+          <t>-10,43; -2,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-12,69; -1,83</t>
+          <t>-6,41; 1,19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,44</t>
+          <t>1,83; 8,43</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -3,76</t>
+          <t>-9,37; -3,39</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-9,7; -1,54</t>
+          <t>-5,27; 0,42</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-17,7%</t>
+          <t>-15,86%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-40,5%</t>
+          <t>-17,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-30,91%</t>
+          <t>-16,62%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 71,18</t>
+          <t>-1,88; 71,61</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-63,52; -20,63</t>
+          <t>-63,27; -19,43</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-40,37; 11,97</t>
+          <t>-39,01; 11,79</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6,91; 80,54</t>
+          <t>7,17; 80,34</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-58,97; -13,07</t>
+          <t>-61,95; -17,16</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-77,0; -13,87</t>
+          <t>-36,64; 8,77</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,34; 61,51</t>
+          <t>9,87; 60,35</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-57,75; -26,88</t>
+          <t>-57,04; -24,65</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-57,7; -11,37</t>
+          <t>-31,37; 3,27</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-3,82</t>
+          <t>-3,9</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-3,41</t>
+          <t>-2,31</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,51; 8,15</t>
+          <t>0,9; 8,32</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 7,12</t>
+          <t>0,28; 7,15</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 0,79</t>
+          <t>-3,64; 2,36</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 6,58</t>
+          <t>-1,52; 6,74</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 2,67</t>
+          <t>-4,97; 2,57</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -0,79</t>
+          <t>-7,65; -0,64</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,37</t>
+          <t>0,64; 6,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,78</t>
+          <t>-1,74; 3,75</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,88; -0,88</t>
+          <t>-4,83; -0,28</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-27,41%</t>
+          <t>-5,61%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-28,77%</t>
+          <t>-29,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-31,25%</t>
+          <t>-21,21%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>4,77; 120,2</t>
+          <t>4,48; 116,82</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>0,69; 110,05</t>
+          <t>2,21; 109,0</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-69,16; 10,27</t>
+          <t>-36,19; 35,12</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 59,89</t>
+          <t>-10,15; 60,43</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 24,35</t>
+          <t>-32,78; 23,14</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-45,94; -7,15</t>
+          <t>-48,07; -6,1</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,36; 67,97</t>
+          <t>5,08; 63,77</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 39,3</t>
+          <t>-14,33; 38,49</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-58,37; -9,72</t>
+          <t>-37,45; -2,44</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-4,03</t>
+          <t>-3,22</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-5,01</t>
+          <t>-4,07</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-4,57</t>
+          <t>-3,69</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,1</t>
+          <t>-0,31; 3,38</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -1,24</t>
+          <t>-4,65; -1,08</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,82; -2,38</t>
+          <t>-5,04; -1,39</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,12; 4,18</t>
+          <t>-0,07; 3,99</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,38; -2,67</t>
+          <t>-6,26; -2,52</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -3,15</t>
+          <t>-5,67; -2,41</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,1</t>
+          <t>0,34; 3,19</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-5,13; -2,42</t>
+          <t>-5,15; -2,37</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-6,17; -3,27</t>
+          <t>-4,86; -2,36</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-29,68%</t>
+          <t>-23,71%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-31,08%</t>
+          <t>-25,2%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-30,6%</t>
+          <t>-24,69%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 24,38</t>
+          <t>-2,47; 26,24</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-32,58; -9,71</t>
+          <t>-32,01; -8,31</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-46,88; -18,62</t>
+          <t>-33,48; -10,89</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>0,72; 27,54</t>
+          <t>-0,54; 26,34</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-37,63; -17,64</t>
+          <t>-37,33; -17,17</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-44,52; -21,06</t>
+          <t>-33,01; -16,23</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,17; 21,78</t>
+          <t>2,06; 22,1</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-32,71; -16,9</t>
+          <t>-32,3; -16,15</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-40,68; -22,82</t>
+          <t>-31,14; -17,03</t>
         </is>
       </c>
     </row>
